--- a/Result/profitability/8109.xlsx
+++ b/Result/profitability/8109.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4375</v>
+        <v>1.515</v>
       </c>
       <c r="N2" t="n">
-        <v>49.1525</v>
+        <v>49.35375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3875</v>
+        <v>1.4825</v>
       </c>
       <c r="N3" t="n">
-        <v>49.16625000000001</v>
+        <v>49.54</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.39625</v>
+        <v>1.45875</v>
       </c>
       <c r="N4" t="n">
-        <v>48.89375</v>
+        <v>49.15499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.33125</v>
+        <v>1.47</v>
       </c>
       <c r="N5" t="n">
-        <v>49.0125</v>
+        <v>49.2075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.78</v>
       </c>
       <c r="M6" t="n">
-        <v>1.30625</v>
+        <v>1.33875</v>
       </c>
       <c r="N6" t="n">
-        <v>48.93</v>
+        <v>49.04375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1775</v>
+        <v>1.21625</v>
       </c>
       <c r="N7" t="n">
-        <v>48.83</v>
+        <v>48.8825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1.055</v>
+        <v>1.0975</v>
       </c>
       <c r="N8" t="n">
-        <v>48.82625</v>
+        <v>48.885</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.9062500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>48.21</v>
+        <v>48.20999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.9012500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>48.21749999999999</v>
+        <v>48.2175</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.85625</v>
       </c>
       <c r="N13" t="n">
-        <v>48.2425</v>
+        <v>48.24250000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>551</v>
+      </c>
+      <c r="D75" t="n">
+        <v>272</v>
+      </c>
+      <c r="E75" t="n">
+        <v>279</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>201</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>36.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>205</v>
+      </c>
+      <c r="K75" t="n">
+        <v>170</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.32375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1942857142857142</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.009379365396128492</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.13265306122449</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.559999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03182374541003652</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
